--- a/data/dictionary.xlsx
+++ b/data/dictionary.xlsx
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Парыж, выдавецтва Грасэ.</t>
+          <t>Парыж, выдавецтва Грасе.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2148,107 +2148,107 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Paris, Verlag Grasset.</t>
+          <t>Jacques Rouxel. Von Kopf bis Fuß.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Paris, Grasset publishing house.</t>
+          <t>The Great Sorcerer said that rockets</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Paris, Grasset publishing house.</t>
+          <t>The Great Sorcerer said that rockets</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">          París, editorial Grasset.</t>
+          <t>París, Editorial Grasset.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">          París, editorial Grasset.</t>
+          <t>París, Editorial Grasset.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Pariis, kirjastus Grasset.</t>
+          <t>Suur võlur ütles, et raketid ebaõnnestu</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Paris, éditions Grasset.</t>
+          <t>Jacques Rouxel. La perfection à l'enver</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Paris, éditions Grasset.</t>
+          <t>Jacques Rouxel. La perfection à l'enver</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Parigi, casa editrice Grasset.</t>
+          <t>Jacques Rouxel. La perfezione al</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">          パリ、グラッセ出版社。</t>
+          <t>畑で育つ植物から収穫されます。</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Париж, Грассе баспасы.</t>
+          <t>Париж, Грассе баспасы.</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve">          파리, 그라세 출판사.</t>
+          <t>때문이라고 했습니다. 하지만 기비들은</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Paryžius, „Grasset“ leidykla.</t>
+          <t>trūksta tranzistorių. Tačiau pas Gibius</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Parīze, izdevniecība Grasset.</t>
+          <t>neveiksmi tāpēc, ka drošības sistēmās</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Parijs, uitgeverij Grasset.</t>
+          <t>De Grote Tovenaar zei dat raketten fale</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Paryż, wydawnictwo Grasset.</t>
+          <t>Wielki czarodziej powiedział, że rakiet</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Paris, editora Grasset.</t>
+          <t>Paris, editora Grasset.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Paris, editora Grasset.</t>
+          <t>Paris, editora Grasset.</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Париж, видавництво Грассе.</t>
+          <t>Великий чаклун сказав, що ракети</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t xml:space="preserve">          巴黎, 格拉塞出版社。</t>
+          <t>菜园里生长的植物上收获的。</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t xml:space="preserve">          巴黎, 格拉塞出版社。</t>
+          <t>菜園裡生長的植物上收穫的。</t>
         </is>
       </c>
     </row>
@@ -14702,6 +14702,116 @@
           <t>Файл повреждён и не может быть установлен. Не найдена сигнатура PFS0</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Файл пашкоджаны і не можа быць усталяваны. Не знойдзена сігнатура PFS0</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Datei beschädigt und kann nicht installiert werden. PFS0-Signatur nicht gefunden</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>File is corrupted and cannot be installed. PFS0 signature not found</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>File is corrupted and cannot be installed. PFS0 signature not found</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>El archivo está dañado y no se puede instalar. No se ha encontrado la firma PFS0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>El archivo está dañado y no se puede instalar. No se encontró la firma PFS0</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Fail on rikutud ja seda ei saa installida. PFS0 signatuuri ei leitud</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Le fichier est corrompu et ne peut pas être installé. Signature PFS0 non trouvée</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Le fichier est corrompu et ne peut pas être installé. Signature PFS0 non trouvée</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Il file è danneggiato e non può essere installato. Firma PFS0 non trovata</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>ファイルが破損しているためインストールできません。PFS0署名が見つかりません</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Файл зақымдалған және орнату мүмкін емес. PFS0 қолтаңбасы табылмады</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>파일이 손상되어 설치할 수 없습니다. PFS0 서명을 찾을 수 없습니다</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Failas sugadintas ir jo negalima įdiegti. PFS0 parašas nerastas</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>Fails ir bojāts un to nevar instalēt. PFS0 paraksts nav atrasts</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>Bestand is beschadigd en kan niet worden geïnstalleerd. PFS0-handtekening niet gevonden</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>Plik jest uszkodzony i nie można go zainstalować. Nie znaleziono sygnatury PFS0</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>O ficheiro está corrompido e não pode ser instalado. Assinatura PFS0 não encontrada</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>O arquivo está corrompido e não pode ser instalado. Assinatura PFS0 não encontrada</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Файл пошкоджено і його неможливо встановити. Не знайдено сигнатуру PFS0</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>文件已损坏，无法安装。未找到PFS0签名</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>檔案已損壞，無法安裝。找不到 PFS0 簽章</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -14709,6 +14819,116 @@
           <t>Файл слишком большой для хранилища</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Файл занадта вялікі для сховішча</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Datei ist zu groß für den Speicher</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>File is too large for storage</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>File is too large for storage</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>El archivo es demasiado grande para el almacenamiento</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>El archivo es demasiado grande para el almacenamiento</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Fail on salvestusruumi jaoks liiga suur</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Le fichier est trop volumineux pour le stockage</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Le fichier est trop volumineux pour le stockage</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Il file è troppo grande per l'archiviazione</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>ストレージに対してファイルが大きすぎます</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Файл сақтау орны үшін тым үлкен</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>파일이 저장소에 비해 너무 큽니다</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Failas per didelis saugyklai</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>Fails ir pārāk liels krātuvei</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>Bestand is te groot voor opslag</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>Plik jest zbyt duży dla pamięci masowej</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>O ficheiro é demasiado grande para o armazenamento</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>O arquivo é muito grande para o armazenamento</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Файл занадто великий для сховища</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>文件对于存储空间来说太大</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>檔案對於儲存空間來說太大</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -14716,6 +14936,116 @@
           <t>Файл: {}</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Файл: {}</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Datei: {}</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>File: {}</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>File: {}</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Archivo: {}</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Archivo: {}</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Fail: {}</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Fichier : {}</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Fichier : {}</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>File: {}</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>ファイル: {}</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Файл: {}</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>파일: {}</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Failas: {}</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>Fails: {}</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>Bestand: {}</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>Plik: {}</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Ficheiro: {}</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Arquivo: {}</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Файл: {}</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>文件: {}</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>檔案: {}</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -14723,6 +15053,116 @@
           <t>Фиксация ФС...</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Фіксацыя ФС...</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Dateisystem-Commit...</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>FS commit...</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>FS commit...</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Confirmación del sistema de archivos...</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Confirmación del sistema de archivos...</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>FS commit...</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Validation du système de fichiers...</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Validation du système de fichiers...</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Commit del file system...</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>ファイルシステムをコミット中...</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>ФС тіркеу...</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>파일 시스템 커밋...</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>FS įrašymas...</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>FS apstiprināšana...</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>Bestandssysteem commit...</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>Zatwierdzanie systemu plików...</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Confirmação do sistema de ficheiros...</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Confirmação do sistema de arquivos...</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Фіксація ФС...</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>文件系统提交...</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>檔案系統提交...</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -14730,6 +15170,116 @@
           <t>Финальный размер: {}</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Канчатковы памер: {}</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Endgröße: {}</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Final size: {}</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Final size: {}</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Tamaño final: {}</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Tamaño final: {}</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Lõplik suurus: {}</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Taille finale : {}</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Taille finale : {}</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Dimensione finale: {}</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>最終サイズ: {}</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Түпкілікті өлшемі: {}</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>최종 크기: {}</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Galutinis dydis: {}</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>Galīgais izmērs: {}</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>Definitieve grootte: {}</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>Rozmiar końcowy: {}</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Tamanho final: {}</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Tamanho final: {}</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Кінцевий розмір: {}</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>最终大小: {}</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>最終大小: {}</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -14737,6 +15287,116 @@
           <t>Формирование списка...</t>
         </is>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Фарміраванне спіса...</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Liste wird erstellt...</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Generating list...</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Generating list...</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Generando lista...</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Generando lista...</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Loendi genereerimine...</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Génération de la liste...</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Génération de la liste...</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Generazione lista...</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>リストを生成中...</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Тізімді құру...</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>목록 생성 중...</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Generuojamas sąrašas...</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>Tiek ģenerēts saraksts...</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>Lijst genereren...</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>Generowanie listy...</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>A gerar lista...</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Gerando lista...</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Формування списку...</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>正在生成列表...</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>正在產生列表...</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -14744,6 +15404,116 @@
           <t>Форсированный язык    : {}</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Фарсіраваная мова    : {}</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Erzwungene Sprache    : {}</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Forced language    : {}</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Forced language    : {}</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Idioma forzado    : {}</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Idioma forzado    : {}</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Sunnitud keel    : {}</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Langue forcée    : {}</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Langue forcée    : {}</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Lingua forzata    : {}</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>強制言語    : {}</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Мәжбүрлі тіл    : {}</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>강제 언어    : {}</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Priverstinė kalba    : {}</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>Piespiedu valoda    : {}</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>Geforceerde taal    : {}</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>Wymuszony język    : {}</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Idioma forçado    : {}</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Idioma forçado    : {}</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Форсована мова    : {}</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>强制语言    : {}</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>強制語言    : {}</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -14751,6 +15521,116 @@
           <t>Форсированный язык    : {} ({})</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Фарсіраваная мова    : {} ({})</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Erzwungene Sprache    : {} ({})</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Forced language    : {} ({})</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Forced language    : {} ({})</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Idioma forzado    : {} ({})</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Idioma forzado    : {} ({})</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Sunnitud keel    : {} ({})</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Langue forcée    : {} ({})</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Langue forcée    : {} ({})</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Lingua forzata    : {} ({})</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>強制言語    : {} ({})</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Мәжбүрлі тіл    : {} ({})</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>강제 언어    : {} ({})</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Priverstinė kalba    : {} ({})</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>Piespiedu valoda    : {} ({})</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>Geforceerde taal    : {} ({})</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>Wymuszony język    : {} ({})</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Idioma forçado    : {} ({})</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Idioma forçado    : {} ({})</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Форсована мова    : {} ({})</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>强制语言    : {} ({})</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>強制語言    : {} ({})</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -14758,6 +15638,116 @@
           <t xml:space="preserve">  Автоопределение</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Аўтавызначэнне</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Automatisch erkennen</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Auto-detect</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Auto-detect</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Detección automática</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Detección automática</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Automaatne tuvastus</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Détection automatique</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Détection automatique</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Rilevamento automatico</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  自動検出</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Автоанықтау</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  자동 감지</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Automatinis aptikimas</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Automātiskā noteikšana</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Automatisch detecteren</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Autodetekcja</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Deteção automática</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Detecção automática</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Автовизначення</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  自动检测</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  自動偵測</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -14765,6 +15755,116 @@
           <t>Форсировано вклчение USB 3.0: {}</t>
         </is>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Фарсіраванае ўключэнне USB 3.0: {}</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>USB 3.0 erzwungen: {}</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Force USB 3.0 enabled: {}</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Force USB 3.0 enabled: {}</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Forzar USB 3.0 habilitado: {}</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Forzar USB 3.0 habilitado: {}</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Sunnitud USB 3.0 lubatud: {}</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Forcer USB 3.0 activé : {}</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Forcer USB 3.0 activé : {}</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Forza USB 3.0 abilitato: {}</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>USB 3.0強制有効: {}</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>USB 3.0 мәжбүрлі қосу: {}</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>USB 3.0 강제 활성화: {}</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Priverstinis USB 3.0 įjungimas: {}</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>USB 3.0 piespiedu iespējošana: {}</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>USB 3.0 gedwongen ingeschakeld: {}</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>Wymuszenie USB 3.0 włączone: {}</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Forçar USB 3.0 ativado: {}</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Forçar USB 3.0 ativado: {}</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Форсоване увімкнення USB 3.0: {}</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>强制开启 USB 3.0: {}</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>強制開啟 USB 3.0: {}</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -14772,6 +15872,116 @@
           <t>Форсировать UTF-8</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Фарсіраваць UTF-8</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>UTF-8 erzwingen</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Force UTF-8</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Force UTF-8</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Forzar UTF-8</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Forzar UTF-8</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Sunni UTF-8</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Forcer UTF-8</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Forcer UTF-8</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Forza UTF-8</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>UTF-8を強制</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>UTF-8 мәжбүрлеу</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>UTF-8 강제</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Priverstinai naudoti UTF-8</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>Uzspiest UTF-8</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>Forceer UTF-8</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>Wymuś UTF-8</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Forçar UTF-8</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Forçar UTF-8</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Форсувати UTF-8</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>强制使用 UTF-8</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>強制使用 UTF-8</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -14779,6 +15989,116 @@
           <t>Форсировать язык</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Фарсіраваць мову</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Sprache erzwingen</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Force language</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Force language</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Forzar idioma</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Forzar idioma</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Sunni keel</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Forcer la langue</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Forcer la langue</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Forza lingua</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>言語を強制</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Тілді мәжбүрлеу</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>언어 강제</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Priverstinai naudoti kalbą</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>Uzspiest valodu</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>Forceer taal</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>Wymuś język</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Forçar idioma</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Forçar idioma</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Форсувати мову</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>强制语言</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>強制語言</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -14786,6 +16106,116 @@
           <t>Французский</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Французская</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Französisch</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Francés</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Francés</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Prantsuse</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Français</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Français</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Francese</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>フランス語</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Француз тілі</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>프랑스어</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Prancūzų</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>Franču</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>Frans</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>Francuski</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Francês</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Francês</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Французька</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>法语</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>法語</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -14793,6 +16223,116 @@
           <t>Х:{}, Т:{}, РЦ:{}</t>
         </is>
       </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Х:{}, Т:{}, РЦ:{}</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>H:{}, T:{}, R:{}</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>H:{}, T:{}, R:{}</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>H:{}, T:{}, R:{}</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>H:{}, T:{}, R:{}</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>H:{}, T:{}, R:{}</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>H:{}, T:{}, R:{}</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>H:{}, T:{}, R:{}</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>H:{}, T:{}, R:{}</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>H:{}, T:{}, R:{}</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>H:{}, T:{}, R:{}</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>H:{}, T:{}, R:{}</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>H:{}, T:{}, R:{}</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>H:{}, T:{}, R:{}</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>H:{}, T:{}, R:{}</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>H:{}, T:{}, R:{}</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>H:{}, T:{}, R:{}</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>H:{}, T:{}, R:{}</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>H:{}, T:{}, R:{}</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>H:{}, T:{}, R:{}</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>H:{}, T:{}, R:{}</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>H:{}, T:{}, R:{}</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -14800,6 +16340,116 @@
           <t>Хранилища MTP</t>
         </is>
       </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Сховішчы MTP</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>MTP-Speicher</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>MTP storage</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>MTP storage</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Almacenamiento MTP</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Almacenamiento MTP</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>MTP-salvestusruum</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Stockage MTP</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Stockage MTP</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Archiviazione MTP</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>MTPストレージ</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>MTP қоймалары</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>MTP 저장소</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>MTP saugykla</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>MTP krātuve</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>MTP-opslag</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>Pamięć MTP</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Armazenamento MTP</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Armazenamento MTP</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Сховища MTP</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>MTP 存储</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>MTP 儲存空間</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -14807,6 +16457,116 @@
           <t>Хранилище только для чтения</t>
         </is>
       </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Сховішча толькі для чытання</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Schreibgeschützter Speicher</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Read-only storage</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Read-only storage</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Almacenamiento de solo lectura</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Almacenamiento de solo lectura</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Kirjutuskaitstud salvestusruum</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Stockage en lecture seule</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Stockage en lecture seule</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Archiviazione di sola lettura</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>読み取り専用ストレージ</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Тек оқуға арналған қойма</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>읽기 전용 저장소</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Tik skaitymo saugykla</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>Tikai lasāma krātuve</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>Alleen-lezen opslag</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>Pamięć tylko do odczytu</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Armazenamento só de leitura</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Armazenamento somente leitura</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Сховище лише для читання</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>只读存储</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>唯讀儲存空間</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -14814,6 +16574,116 @@
           <t>Хэш версии              : {}</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Хэш версіі              : {}</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Versions-Hash           : {}</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Version hash            : {}</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Version hash            : {}</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Hash de la versión      : {}</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Hash de la versión      : {}</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Versiooni räsi          : {}</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Hash de la version      : {}</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Hash de la version      : {}</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Hash della versione     : {}</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>バージョンハッシュ      : {}</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Нұсқа хэші              : {}</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>버전 해시               : {}</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Versijos maiša          : {}</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>Versijas hešs           : {}</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>Versie-hash             : {}</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>Hash wersji             : {}</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Hash da versão          : {}</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Hash da versão          : {}</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Хеш версії              : {}</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>版本哈希                : {}</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>版本雜湊                : {}</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -14821,6 +16691,116 @@
           <t>Целевая запись о контенте не найдена</t>
         </is>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Мэтавы запіс пра кантэнт не знойдзены</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Zieldatensatz für den Inhalt nicht gefunden</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Target content record not found</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Target content record not found</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Registro de contenido de destino no encontrado</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Registro de contenido de destino no encontrado</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Sihtsisukirjet ei leitud</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Enregistrement de contenu cible non trouvé</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Enregistrement de contenu cible non trouvé</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Record del contenuto di destinazione non trovato</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>ターゲットコンテンツレコードが見つかりません</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Мақсатты мазмұн жазбасы табылмады</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>대상 콘텐츠 레코드를 찾을 수 없습니다</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Tikslinis turinio įrašas nerastas</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>Mērķa satura ieraksts nav atrasts</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>Doelinhoudrecord niet gevonden</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>Docelowy rekord zawartości nie został znaleziony</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Registro de conteúdo de destino não encontrado</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Registro de conteúdo de destino não encontrado</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Цільовий запис про контент не знайдено</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>未找到目标内容记录</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>找不到目標內容記錄</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -14828,6 +16808,116 @@
           <t>ЧАСТЬ КОНТЕНТА ОТСУТСТВУЕТ. ИГРА НЕ БУДЕТ РАБОТАТЬ</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>ЧАСТКА КАНТЭНТУ АДСУТНІЧАЕ. ГУЛЬНЯ НЕ БУДЗЕ ПРАЦАВАЦЬ</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>TEILE DES INHALTS FEHLEN. DAS SPIEL WIRD NICHT FUNKTIONIEREN</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>PART OF THE CONTENT IS MISSING. THE GAME WILL NOT WORK</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>PART OF THE CONTENT IS MISSING. THE GAME WILL NOT WORK</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>FALTA PARTE DEL CONTENIDO. EL JUEGO NO FUNCIONARÁ</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>FALTA PARTE DEL CONTENIDO. EL JUEGO NO FUNCIONARÁ</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>OSA SISUST ON PUUDU. MÄNG EI TÖÖTA</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>UNE PARTIE DU CONTENU EST MANQUANTE. LE JEU NE FONCTIONNERA PAS</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>UNE PARTIE DU CONTENU EST MANQUANTE. LE JEU NE FONCTIONNERA PAS</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>PARTE DEL CONTENUTO MANCANTE. IL GIOCO NON FUNZIONERÀ</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>コンテンツの一部が不足しています。ゲームは動作しません</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>МАЗМҰН БӨЛІГІ ЖОҚ. ОЙЫН ЖҰМЫС ІСТЕМЕЙДІ</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>콘텐츠 일부가 누락되었습니다. 게임이 작동하지 않습니다</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>DALIS TURINIO TRŪKSTA. ŽAIDIMAS NEVEIKS</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>TRŪKST DAĻAS SATURA. SPĒLE NEDARBOSIES</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>EEN DEEL VAN DE INHOUD ONTBREEKT. HET SPEL ZAL NIET WERKEN</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>BRAKUJE CZĘŚCI ZAWARTOŚCI. GRA NIE BĘDZIE DZIAŁAĆ</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>PARTE DO CONTEÚDO ESTÁ EM FALTA. O JOGO NÃO IRÁ FUNCIONAR</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>PARTE DO CONTEÚDO ESTÁ FALTANDO. O JOGO NÃO VAI FUNCIONAR</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>ЧАСТИНА КОНТЕНТУ ВІДСУТНЯ. ГРА НЕ ПРАЦЮВАТИМЕ</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>部分内容缺失。游戏将无法运行</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>部分內容缺失。遊戲將無法執行</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -14835,6 +16925,116 @@
           <t>Число транзисторов: {:&gt;3}</t>
         </is>
       </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Колькасць транзістараў: {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Anzahl der Transistoren: {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Number of transistors: {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Number of transistors: {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Número de transistores: {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Número de transistores: {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Transistorite arv: {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Nombre de transistors : {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Nombre de transistors : {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Numero di transistor: {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>トランジスタ数: {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Транзисторлар саны: {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>트랜지스터 수: {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Tranzistorių skaičius: {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>Tranzistoru skaits: {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>Aantal transistoren: {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>Liczba tranzystorów: {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Número de transístores: {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Número de transistores: {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Кількість транзисторів: {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>晶体管数量: {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>電晶體數量: {:&gt;3}</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -14842,6 +17042,116 @@
           <t>Число уникальных сыграных игр : {}</t>
         </is>
       </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Колькасць унікальных згуляных гульняў : {}</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Anzahl der einzigartig gespielten Spiele : {}</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Number of unique games played : {}</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Number of unique games played : {}</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Número de juegos únicos jugados : {}</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Número de juegos únicos jugados : {}</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Mängitud unikaalsete mängude arv : {}</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Nombre de jeux uniques joués : {}</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Nombre de jeux uniques joués : {}</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Numero di giochi unici giocati : {}</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>プレイしたユニークなゲーム数 : {}</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Ойналған бірегей ойындар саны : {}</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>플레이한 고유 게임 수 : {}</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Unikalių žaistų žaidimų skaičius : {}</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>Unikālo spēlēto spēļu skaits : {}</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>Aantal unieke gespeelde spellen : {}</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>Liczba unikalnych rozegranych gier : {}</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Número de jogos únicos jogados : {}</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Número de jogos únicos jogados : {}</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Кількість унікальних зіграних ігор : {}</t>
+        </is>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>已玩独特游戏数量 : {}</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>已玩獨特遊戲數量 : {}</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -14849,6 +17159,116 @@
           <t>Число ходов:        {:&gt;3}</t>
         </is>
       </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Колькасць хадоў:        {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Anzahl der Züge:        {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Number of moves:        {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Number of moves:        {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Número de movimientos:  {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Número de movimientos:  {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Käikude arv:            {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Nombre de coups :       {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Nombre de coups :       {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Numero di mosse:        {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>ターン数:               {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Жүрістер саны:          {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>턴 수:                  {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Ėjimų skaičius:         {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>Gājienu skaits:         {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>Aantal zetten:          {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>Liczba ruchów:          {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Número de movimentos:   {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Número de movimentos:   {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Кількість ходів:        {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>回合数:                 {:&gt;3}</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>回合數:                 {:&gt;3}</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -14856,6 +17276,116 @@
           <t>Читать дату файлов</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Чытаць дату файлаў</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Dateidatum lesen</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Read file date</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Read file date</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Leer fecha de archivo</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Leer fecha de archivo</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Lugeda faili kuupäeva</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Lire la date du fichier</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Lire la date du fichier</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Leggi data file</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>ファイルの日付を読み取る</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Файл күнін оқу</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>파일 날짜 읽기</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Nuskaityti failo datą</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>Lasīt faila datumu</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>Bestandsdatum lezen</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>Odczytaj datę pliku</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Ler data do ficheiro</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Ler data do arquivo</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Читати дату файлів</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>读取文件日期</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>讀取檔案日期</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -14863,6 +17393,116 @@
           <t>Чтение каталога...</t>
         </is>
       </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Чытанне каталога...</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Verzeichnis wird gelesen...</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Reading directory...</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Reading directory...</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Leyendo directorio...</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Leyendo directorio...</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Kataloogi lugemine...</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Lecture du répertoire...</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Lecture du répertoire...</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Lettura directory in corso...</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>ディレクトリを読み込み中...</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Каталогты оқу...</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>디렉토리 읽는 중...</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Skaitomas katalogas...</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>Notiek kataloga nolasīšana...</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>Map lezen...</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>Odczytywanie katalogu...</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>A ler diretório...</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Lendo diretório...</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Читання каталогу...</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>正在读取目录...</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>正在讀取目錄...</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -14870,6 +17510,116 @@
           <t>Чтение списка файлов...</t>
         </is>
       </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Чытанне спісу файлаў...</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Dateiliste wird gelesen...</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Reading file list...</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Reading file list...</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Leyendo lista de archivos...</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Leyendo lista de archivos...</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Faililoendi lugemine...</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Lecture de la liste des fichiers...</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Lecture de la liste des fichiers...</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Lettura elenco file in corso...</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>ファイルリストを読み込み中...</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Файлдар тізімін оқу...</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>파일 목록 읽는 중...</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Skaitomas failų sąrašas...</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>Notiek failu saraksta nolasīšana...</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>Bestandslijst lezen...</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>Odczytywanie listy plików...</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>A ler lista de ficheiros...</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Lendo lista de arquivos...</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Читання списку файлів...</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>正在读取文件列表...</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>正在讀取檔案列表...</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -14877,6 +17627,116 @@
           <t>Что-то плохое грядёт</t>
         </is>
       </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Нешта кепскае насоўваецца</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Etwas Schlimmes kommt auf uns zu</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Something bad is coming</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Something bad is coming</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Algo malo se acerca</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Algo malo se acerca</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Midagi halba on tulemas</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Quelque chose de mauvais arrive</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Quelque chose de mauvais arrive</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Qualcosa di brutto sta arrivando</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>何か悪いことが起きようとしている</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Жаман нәрсе келе жатыр</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>뭔가 나쁜 일이 다가오고 있습니다</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Artėja kažkas blogo</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>Kaut kas slikts tuvojas</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>Er komt iets ergs aan</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>Coś złego nadchodzi</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Algo de mau está a chegar</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Algo ruim está vindo</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Щось погане насувається</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>不祥之事即将发生</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>不祥之事即將發生</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -14884,6 +17744,116 @@
           <t>Что-то пошло не так. Пропускаем оставшийся файл</t>
         </is>
       </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Нешта пайшло не так. Прапускаем астатні файл</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Etwas ist schief gelaufen. Die verbleibende Datei wird übersprungen</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Something went wrong. Skipping the remaining file</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Something went wrong. Skipping the remaining file</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Algo salió mal. Saltando el archivo restante</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Algo salió mal. Saltando el archivo restante</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Midagi läks valesti. Jätan ülejäänud faili vahele</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Quelque chose a mal tourné. Passage du fichier restant</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Quelque chose a mal tourné. Passage du fichier restant</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Qualcosa è andato storto. Saltando il file rimanente</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>何かがうまくいきませんでした。残りのファイルをスキップします</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Бірдеңе дұрыс болмады. Қалған файлды өткізіп жіберу</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>문제가 발생했습니다. 나머지 파일을 건너뜁니다</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Įvyko klaida. Praleidžiamas likęs failas</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>Kaut kas nogāja greizi. Izlaižu atlikušo failu</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>Er is iets misgegaan. Het resterende bestand wordt overgeslagen</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>Coś poszło nie tak. Pomijam pozostały plik</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Algo correu mal. A saltar o ficheiro restante</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Algo deu errado. Pulando o arquivo restante</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Щось пішло не так. Пропускаємо файл, що залишився</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>出错了。正在跳过剩余文件</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>出錯了。正在跳過剩餘檔案</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -14891,6 +17861,116 @@
           <t>Чтобы вернуться, нажмите B</t>
         </is>
       </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Каб вярнуцца, націсніце B</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Drücken Sie B, um zurückzukehren</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Press B to go back</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Press B to go back</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Pulsa B para volver</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Presiona B para volver</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Tagasiminemiseks vajutage B</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Appuyez sur B pour revenir</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Appuyez sur B pour revenir</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Premi B per tornare indietro</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Bボタンを押して戻る</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Кері қайту үшін B батырмасын басыңыз</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>돌아가려면 B를 누르세요</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Norėdami grįžti, paspauskite B</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>Lai atgrieztos, nospiediet B</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>Druk op B om terug te keren</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>Naciśnij B, aby wrócić</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Prima B para voltar</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Pressione B para voltar</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Щоб повернутися, натисніть B</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>按 B 返回</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>按 B 返回</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -14898,6 +17978,116 @@
           <t>Шадок у Гиби</t>
         </is>
       </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Шадок у Гібі</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Shadok bei Gibi</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Shadok at Gibi</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Shadok at Gibi</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Shadok en Gibi</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Shadok en Gibi</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Shadok Gibis</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Shadok chez Gibi</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Shadok chez Gibi</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Shadok da Gibi</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>ギビのシャドック</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Гибидегі Шадок</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>기비의 샤독</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Šadokas pas Gibį</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>Šadoks pie Gibi</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>Shadok bij Gibi</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>Shadok u Gibiego</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Shadok em Gibi</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Shadok em Gibi</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Шадок у Гібі</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>吉比的沙多克</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>吉比的沙多克</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -14905,6 +18095,116 @@
           <t xml:space="preserve">Шифрование секции </t>
         </is>
       </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Шыфраванне секцыі</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Verschlüsselung des Abschnitts</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Section encryption</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Section encryption</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Cifrado de sección</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Cifrado de sección</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Sektsiooni krüpteerimine</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Chiffrement de la section</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Chiffrement de la section</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Cifratura della sezione</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>セクションの暗号化</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Секцияны шифрлау</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>섹션 암호화</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Sekcijos šifravimas</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>Sekcijas šifrēšana</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Versleuteling van sectie</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>Szyfrowanie sekcji</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Cifragem da secção</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Criptografia da seção</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Шифрування секції</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>段加密</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>區段加密</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -14912,6 +18212,116 @@
           <t>Экзосфера очищает CAL0      : {}</t>
         </is>
       </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Экзасфера ачышчае CAL0      : {}</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Exosphäre bereinigt CAL0      : {}</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Exosphere clearing CAL0      : {}</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Exosphere clearing CAL0      : {}</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>La exosfera limpia CAL0      : {}</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>La exosfera limpia CAL0      : {}</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Eksofiir puhastab CAL0      : {}</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>L'exosphère nettoie CAL0      : {}</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>L'exosphère nettoie CAL0      : {}</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>L'esosfera pulisce CAL0      : {}</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>外気圏がCAL0を消去中      : {}</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Экзосфера CAL0 тазартуда      : {}</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>외기권이 CAL0 삭제 중      : {}</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Egzosfera valo CAL0      : {}</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>Eksosfēra tīra CAL0      : {}</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>Exosfeer wist CAL0      : {}</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>Egzosfera czyści CAL0      : {}</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>A exosfera limpa CAL0      : {}</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>A exosfera limpa CAL0      : {}</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Екзосфера очищує CAL0      : {}</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>外逸层正在清除 CAL0      : {}</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>外逸層正在清除 CAL0      : {}</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -14919,6 +18329,116 @@
           <t>Экран                 : ({:08X}) {}</t>
         </is>
       </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Экран                 : ({:08X}) {}</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Bildschirm            : ({:08X}) {}</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Screen                : ({:08X}) {}</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Screen                : ({:08X}) {}</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Pantalla              : ({:08X}) {}</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Pantalla              : ({:08X}) {}</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Ekraan                : ({:08X}) {}</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Écran                 : ({:08X}) {}</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Écran                 : ({:08X}) {}</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Schermo               : ({:08X}) {}</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>画面                  : ({:08X}) {}</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Экран                 : ({:08X}) {}</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>화면                  : ({:08X}) {}</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Ekranas               : ({:08X}) {}</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>Ekrāns                : ({:08X}) {}</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>Scherm                : ({:08X}) {}</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>Ekran                 : ({:08X}) {}</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Ecrã                  : ({:08X}) {}</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Tela                  : ({:08X}) {}</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Екран                 : ({:08X}) {}</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>屏幕                  : ({:08X}) {}</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>螢幕                  : ({:08X}) {}</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -14926,6 +18446,116 @@
           <t>Экспорт SDK</t>
         </is>
       </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Экспарт SDK</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>SDK-Export</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>SDK Export</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>SDK Export</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Exportación de SDK</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Exportación de SDK</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>SDK eksport</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Exportation SDK</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Exportation SDK</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Esportazione SDK</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>SDKエクスポート</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>SDK экспорты</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>SDK 내보내기</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>SDK eksportas</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>SDK eksports</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>SDK-export</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>Eksport SDK</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Exportação de SDK</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Exportação de SDK</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Експорт SDK</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>SDK 导出</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>SDK 匯出</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -14933,6 +18563,116 @@
           <t>Экспортировать</t>
         </is>
       </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Экспартаваць</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Exportieren</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Export</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Export</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Exportar</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Exportar</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Ekspordi</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Exporter</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Exporter</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Esporta</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>エクスポート</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Экспорттау</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>내보내기</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Eksportuoti</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Eksportēt</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>Exporteren</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>Eksportuj</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Exportar</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Exportar</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Експортувати</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>导出</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>匯出</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -14940,6 +18680,116 @@
           <t>Экспортировать SDK</t>
         </is>
       </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Экспартаваць SDK</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>SDK exportieren</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Export SDK</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Export SDK</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Exportar SDK</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Exportar SDK</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Ekspordi SDK</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Exporter le SDK</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Exporter le SDK</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Esporta SDK</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>SDKをエクスポート</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>SDK-ны экспорттау</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>SDK 내보내기</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Eksportuoti SDK</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>Eksportēt SDK</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>SDK exporteren</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>Eksportuj SDK</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Exportar SDK</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Exportar SDK</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Експортувати SDK</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>导出 SDK</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>匯出 SDK</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -14947,6 +18797,116 @@
           <t>Это действие будет нельзя отменить</t>
         </is>
       </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Гэта дзеянне нельга будзе адмяніць</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Diese Aktion kann nicht rückgängig gemacht werden</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>This action cannot be undone</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>This action cannot be undone</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Esta acción no se puede deshacer</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Esta acción no se puede deshacer</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Seda toimingut ei saa tagasi võtta</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Cette action ne peut pas être annulée</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Cette action ne peut pas être annulée</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Questa azione non può essere annullata</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>この操作は取り消せません</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Бұл әрекетті болдырмау мүмкін емес</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>이 작업은 취소할 수 없습니다</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Šio veiksmo atšaukti negalima</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>Šo darbību nevar atsaukt</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>Deze actie kan niet ongedaan worden gemaakt</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>Tej czynności nie można cofnąć</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Esta ação não pode ser desfeita</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Esta ação não pode ser desfeita</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Цю дію неможливо буде скасувати</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>此操作无法撤消</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>此操作無法復原</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -14954,6 +18914,116 @@
           <t>Язык                    : {}</t>
         </is>
       </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Мова                    : {}</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Sprache                 : {}</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Language                : {}</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Language                : {}</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Idioma                  : {}</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Idioma                  : {}</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Keel                    : {}</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Langue                  : {}</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Langue                  : {}</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Lingua                  : {}</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>言語                    : {}</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Тіл                     : {}</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>언어                    : {}</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Kalba                   : {}</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>Valoda                  : {}</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>Taal                    : {}</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>Język                   : {}</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Idioma                  : {}</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Idioma                  : {}</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Мова                    : {}</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>语言                    : {}</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>語言                    : {}</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -14961,6 +19031,116 @@
           <t>Январь</t>
         </is>
       </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Студзень</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Januar</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Jaanuar</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Janvier</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Janvier</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Gennaio</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>1月</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>Қаңтар</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>1월</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Sausis</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>Janvāris</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>Januari</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>Styczeń</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Janeiro</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Січень</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>一月</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>一月</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -14989,6 +19169,116 @@
           <t>больше шансов, что оно заработает». Их</t>
         </is>
       </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>«Чым больш няўдач, тым больш шанцаў,</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>ausgedrückt: ‚Je mehr Misserfolge, dest</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>of working.’ Their rocket is still</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>of working.’ Their rocket is still</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>fracasos, más posibilidades de que</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>fracasos, más posibilidades de que</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>et see töötab.“ Nende rakett on veel</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>« Plus il y a d'échecs, plus il y a de</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>« Plus il y a d'échecs, plus il y a de</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>«Più fallimenti ci sono, più</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>それが成功する確率が少なくとも100万分の1は</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>кету мүмкіндігі соғұрлым жоғары». Олард</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>그들은 그것이 작동할 확률이 최소</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>dar netobula, bet jie apskaičiavo, kad</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Viņu raķete vēl ir nepilnīga, bet viņi </t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>dat het werkt.‘ Hun raket is nog</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>że to zadziała”. Ich rakieta jest jeszc</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>fracassos, maior a hipótese de</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>fracassos, mais chances de que</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>шансів, що воно запрацює». Їхня ракета</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>但他们计算出它至少有百万分之一的</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>但他們計算出它至少有百萬分之一的</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -14996,6 +19286,112 @@
           <t>быстро проникли в планы шадоков и</t>
         </is>
       </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>капялюшам, хутка праніклі ў планы</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>schicken, um Transistoren zu suchen.</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>plans and decided to have some fun.</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>plans and decided to have some fun.</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>sombreros, comprendieron rápidamente lo</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>sombreros, comprendieron rápidamente lo</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Shadokil siseneda ühte oma aeda, kuid</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>planète des Gibis pour chercher des</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>planète des Gibis pour chercher des</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>molto intelligenti grazie ai loro</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>арқасында өте ақылды, шадоктардың</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>식물이 꽃을 피워 트랜지스터가 나올 때마다,</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>kiekvieną kartą, kai augalas pražysta i</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>bet ielenca viņu no visām pusēm, un ikr</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>plannen van de Shadoks en besloten om</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>przejrzeli plany Shadoków i postanowili</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>perceberam rapidamente os planos dos</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>perceberam rapidamente os planos dos</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>вирішили розважитися. Вони дозволили</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>他们就冲上前去，赶在沙多克之前收获。</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>他們就衝上前去，趕在沙多克之前收穫。</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -15003,6 +19399,92 @@
           <t>всякий раз, когда растение расцветает</t>
         </is>
       </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>бакоў, і кожны раз, калі расліна</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>sich zu amüsieren. Sie ließen den Shado</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>transistor, they race to harvest it</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>transistor, they race to harvest it</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>rodearon, y cada vez que una planta flo</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>rodearon, y cada vez que una planta flo</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>koristama.</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>de s'amuser. Ils ont laissé le Shadok</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>de s'amuser. Ils ont laissé le Shadok</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>entrasse in uno dei loro orti, ma lo</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>жағынан қоршап алды да, өсімдік гүлдеп,</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr"/>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>een plant bloeit en een transistor</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>razem, gdy roślina zakwita i wydaje</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>sempre que uma planta floresce e dá um</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>lados, e toda vez que uma planta flores</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>транзистор, вони мчать, щоб зібрати</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr"/>
+      <c r="Y161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -15010,6 +19492,116 @@
           <t>выражениях: «Чем больше неудач, тем</t>
         </is>
       </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>поспехам». Ці, іншымі словамі:</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>einem Erfolg zu führen.‘ Oder anders</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>more failures, the more chance it has</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>more failures, the more chance it has</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>O, en otras palabras: «Cuantos más</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>O, en otras palabras: «Cuantos más</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>läbikukkumisi, seda suurem on võimalus,</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>par réussir ». Ou, en d'autres termes :</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>par réussir ». Ou, en d'autres termes :</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>successo». O, in altre parole:</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>彼らのロケットはまだ不完全ですが、彼らは</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>қаншалықты көп болса, оның жұмыс істеп</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>것이죠. 그들의 로켓은 아직 불완전하지만,</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>daugiau šansų, kad tai veiks“. Jų raket</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>jo lielāka iespēja, ka tas nostrādās“.</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>meer mislukkingen, hoe groter de kans</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>więcej niepowodzeń, tym większa szansa,</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Ou, por outras palavras: «Quanto mais</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Ou, em outras palavras: «Quanto mais</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>словами: «Чим більше невдач, тим більше</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>他们的火箭尚不完美，</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>他們的火箭尚不完美，</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -15017,6 +19609,116 @@
           <t>вычислили, что у них есть по крайней</t>
         </is>
       </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>недасканалая, але яны вылічылі, што ў</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Ihre Rakete ist noch unvollkommen, aber</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>that they have at least one chance in a</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>that they have at least one chance in a</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>pero han calculado que tienen al menos</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>pero han calculado que tienen al menos</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>arvutanud, et neil on vähemalt üks</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>est encore imparfaite, mais ils ont</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>est encore imparfaite, mais ils ont</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Il loro razzo è ancora imperfetto, ma</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>失敗を急いで完了させ、100万回目が成功する</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>оны жұмыс істеп кетуі үшін кемінде</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>그래서 그들은 100만 번째에는 확실히</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>ji veiks… Ir jie skuba atlikti pirmuosi</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>iespēja no miljona, ka tā nostrādās…</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>ze minstens één kans op een miljoen</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>przynajmniej jedną szansę na milion, że</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>imperfeito, mas calcularam que têm pelo</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>imperfeito, mas eles calcularam que têm</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>у них є принаймні один шанс із мільйона</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>于是他们急于完成前999999次</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>於是他們急於完成前999999次</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -15031,6 +19733,116 @@
           <t>заработает… И они торопятся поскорее</t>
         </is>
       </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>што яна запрацуе… І яны спяшаюцца</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>eine Chance von einer Million hat, dass</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>hurrying to complete the first 999999</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>hurrying to complete the first 999999</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>funcione... Y se apresuran a completar</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>funcione... Y se apresuran a completar</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>tõttavad kiiresti sooritama esimesed</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>sur un million qu'elle fonctionne...</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>sur un million qu'elle fonctionne...</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>possibilità su un milione che</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>ジャック・ルクセル。『逆転の完成』。</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>есептеді... Олар миллионыншысы</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>실패를 서둘러 끝내려 합니다.»</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>būtų tikri, jog milijonasis veiks“.</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>999999 neveiksmīgos mēģinājumus, lai</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>om de eerste 999999 mislukte pogingen t</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>zrealizować 999999 pierwszych nieudanyc</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>funcione... E estão a apressar-se para</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>que funcione... E eles estão correndo</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>якнайшвидше здійснити 999999 перших</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>雅克·鲁克塞尔。《逆向完美》。</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>雅克·魯克塞爾。《逆向完美》。</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -15038,6 +19850,88 @@
           <t>и дает транзистор, они мчатся, чтобы</t>
         </is>
       </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>расквітае і дае транзістар, яны імчацца</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>in einen ihrer Gärten eindringen, aber</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>before the Shadok.</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>before the Shadok.</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>y da un transistor, corren a recoger la</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>y da un transistor, corren a recoger la</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>entrer dans l'un de leurs jardins, mais</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>entrer dans l'un de leurs jardins, mais</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>hanno circondato e, ogni volta che una</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>транзистор шығарған сайын, олар шадокта</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr"/>
+      <c r="Q166" t="inlineStr"/>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voortbrengt, racen ze om de oogst voor </t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>tranzystor, pędzą, by zebrać plony</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>transístor, eles correm para colher a</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>e produz um transistor, eles correm</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>врожай раніше за шадока.</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr"/>
+      <c r="Y166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -15045,6 +19939,116 @@
           <t>и не кончилось успехом». Или, в других</t>
         </is>
       </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>працягвалася і не скончылася</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>kontinuierlich weitergeht, ohne zu</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>in success.’ Or, in other words: ‘The</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>in success.’ Or, in other words: ‘The</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>indefinidamente sin acabar en éxito».</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>indefinidamente sin acabar en éxito».</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>eduga.“ Või teisisõnu: „Mida rohkem</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>qui continue indéfiniment sans finir</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>qui continue indéfiniment sans finir</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>indefinitamente senza finire con un</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>成功する確率は高くなる』ということです。</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>жоқ». Немесе басқаша айтқанда: «Сәтсізд</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>많을수록 작동할 확률은 더 커진다’는</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>tariant: „Kuo daugiau nesėkmių, tuo</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>vārdiem sakot: „Jo vairāk neveiksmju,</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>te leiden.‘ Of, met andere woorden: ‚Ho</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>sukcesem”. Albo, innymi słowy: „Im</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>indefinidamente sem acabar em sucesso».</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>indefinidamente sem terminar em sucesso</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>закінчилося успіхом». Або, іншими</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>成功的可能性就越大’。</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>成功的可能性就越大’。</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -15052,6 +20056,116 @@
           <t>мере один шанс из миллиона, что она</t>
         </is>
       </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>іх ёсць прынамсі адзін шанец з мільёна,</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>sie haben berechnet, dass sie mindesten</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>million that it will work… And they are</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>million that it will work… And they are</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>una posibilidad entre un millón de que</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>una posibilidad entre un millón de que</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>miljonist võimalus, et see töötab… Ja n</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>calculé qu'ils ont au moins une chance</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>calculé qu'ils ont au moins une chance</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>hanno calcolato che hanno almeno una</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>ことを確実にしようとしています」。</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>миллионнан бір мүмкіндік бар деп</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>작동하게 하려고 앞선 999999번의</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>999999 nesėkmingus bandymus, kad</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>Un viņi steidzas ātrāk īstenot pirmos</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>hebben dat het werkt… En ze haasten zic</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>zadziała… I śpieszą się, by szybciej</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>menos uma hipótese em um milhão de que</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>pelo menos uma chance em um milhão de</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>що вона запрацює… І вони поспішають</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>失败的试验，以确保第100万次会成功。”</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>失敗的試驗，以確保第100萬次會成功。”</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -15059,6 +20173,116 @@
           <t>миллионная заработает».</t>
         </is>
       </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>што мільённая запрацуе».</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>hinter sich zu bringen, um sicher zu</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Jacques Rouxel. Perfection Backwards.</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Jacques Rouxel. Perfection Backwards.</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>funcionará».</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>funcionará».</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Jacques Rouxel. Täiuslikkus tagurpidi.</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>pour être sûrs que le millionième</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>pour être sûrs que le millionième</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>falliti per essere sicuri che il</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>安全システムにトランジスタが足りないからだと</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>аяқтауға асығуда».</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>위대한 마법사는 로켓이 실패하는 이유는</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Didysis burtininkas pasakė, kad raketos</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>Parīze, Grasset izdevniecība.</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>Jacques Rouxel. Perfectie achterstevore</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>Jacques Rouxel. Doskonałość na wspak.</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>milionésima funcionará».</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>que a milionésima funcionará».</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Жак Руксель. Досконалість навиворіт.</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>安全系统中缺少晶体管。</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>安全系統中缺少電晶體。</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -15087,6 +20311,116 @@
           <t>ничего, что бы непрерывно продолжалось</t>
         </is>
       </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>нічога, што б бесперапынна</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Shadok-Logik: ‚Es gibt nichts, was</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>continues indefinitely without ending</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>continues indefinitely without ending</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>«No hay nada que continúe</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>«No hay nada que continúe</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>mis jätkuks lõputult ja ei lõppeks</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>de la logique shadok : « Il n'y a rien</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>de la logique shadok : « Il n'y a rien</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>«Non c'è nulla che continui</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>ということです。あるいは、『失敗すればするほど、</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>ұшырамай үздіксіз жалғасатын ештеңе</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>때문입니다. 다르게 말하면, ‘실패가</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>ir nesibaigtų sėkme“. Arba, kitaip</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>un nebeigtos ar panākumiem“. Vai, citie</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>continu doorgaat zonder tot een succes</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>w nieskończoność i nie skończyło się</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>«Não há nada que continue</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>«Não há nada que continue</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>нічого, що б безперервно тривало і не</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>或者换句话说：‘失败越多，</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>或者換句話說：‘失敗越多，</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -15094,6 +20428,92 @@
           <t>но окружили его со всех сторон, и</t>
         </is>
       </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>іх агародаў, але акружылі яго з усіх</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>die Pläne der Shadoks und beschlossen,</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>time a plant blooms and produces a</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>time a plant blooms and produces a</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>entrara en uno de sus huertos, pero lo</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>entrara en uno de sus huertos, pero lo</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>tormavad nad saaki enne Shadokit ära</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>percé les plans des Shadoks et ont déci</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>percé les plans des Shadoks et ont déci</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>divertirsi. Hanno lasciato che lo Shado</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>біріне кіруге рұқсат берді, бірақ оны ж</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>hem van alle kanten, en telkens wanneer</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>otoczyli go z każdej strony, i za każdy</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>mas rodearam-no de todos os lados e,</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>hortas, mas o rodearam por todos os</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>і щоразу, коли рослина розквітає і дає</t>
+        </is>
+      </c>
+      <c r="X174" t="inlineStr"/>
+      <c r="Y174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -15101,6 +20521,116 @@
           <t>опытов, чтобы быть уверенными, что</t>
         </is>
       </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>няўдалых спроб, каб быць упэўненымі,</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>sich, die ersten 999999 Fehlversuche</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>millionth one will work.”</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>millionth one will work.”</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>para estar seguros de que el millonésim</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>para estar seguros de que el millonésim</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>kindlad, et miljones töötab.“</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>999999 premiers essais infructueux</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>999999 premiers essais infructueux</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>completare i primi 999999 tentativi</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>偉大な魔法使いは、ロケットが失敗するのは</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>алғашқы 999999 сәтсіз тәжірибені тезіре</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>파리, 그라세 출판사.</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Paryžius, „Grasset“ leidykla.</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>Žaks Rušels. Pilnība otrādi.</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>de miljoenste werkt.“</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>zadziała”.</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>falhadas para terem a certeza de que a</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>tentativas falhas para ter certeza de</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>що мільйонна запрацює».</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>大巫师说，火箭失败的原因是</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>大巫師說，火箭失敗的原因是</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -15108,6 +20638,116 @@
           <t>осуществить 999999 первых неудачных</t>
         </is>
       </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>хутчэй ажыццявіць 999999 першых</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>sie funktioniert ... Und sie beeilen</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>failed attempts to be sure that the</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>failed attempts to be sure that the</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>los primeros 999999 intentos fallidos</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>los primeros 999999 intentos fallidos</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>999999 ebaõnnestunud katset, et olla</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Et ils se dépêchent de réaliser les</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Et ils se dépêchent de réaliser les</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>funzioni... E hanno fretta di</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>パリ、グラッセ出版。</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>жұмыс істейтініне көз жеткізу үшін</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>자크 뤼크셀. 거꾸로 된 완벽.</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Jacques Rouxel. Tobulumas atvirkščiai.</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>būtu droši, ka miljonais izdosies“.</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>voltooien om er zeker van te zijn dat</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>prób, by mieć pewność, że milionowa</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>concluir as primeiras 999999 tentativas</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>para completar as primeiras 999999</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>невдалих спроб, щоб бути впевненими,</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>巴黎，格拉塞出版社。</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>巴黎，格拉塞出版社。</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -15115,6 +20755,116 @@
           <t>очень умные благодаря своим шляпам,</t>
         </is>
       </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>вельмі разумныя дзякуючы сваім</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>einen Shadok zum Planeten der Gibis zu</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>hats, quickly realized the Shadoks’</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>hats, quickly realized the Shadoks’</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Gibis, muy inteligentes gracias a sus</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Gibis, muy inteligentes gracias a sus</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>pihta ja otsustasid nalja teha. Nad las</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Il est décidé d'envoyer un Shadok sur l</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Il est décidé d'envoyer un Shadok sur l</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Gibi a cercare transistor. I Gibi,</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>先にそれを収穫するために駆けつけます。</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>қабылданды. Гибилер, қалпақтарының</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>사방에서 그를 에워쌌습니다. 그리고</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>daržų, bet apsupo jį iš visų pusių, ir</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>Šadokam iekļūt vienā no saviem dārziem,</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>zeer intelligent zijn, doorzagen snel d</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>dzięki swoim kapeluszom, szybko</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>inteligentes graças aos seus chapéus,</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>inteligentes graças aos seus chapéus,</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>швидко розгадали плани шадоків і</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>每当植物开花产生晶体管时，</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>每當植物開花產生電晶體時，</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -15122,6 +20872,116 @@
           <t>планету гиби искать транзисторы. Гиби,</t>
         </is>
       </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>планету гібі шукаць транзістары. Гібі,</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>in Gärten wachsen. Es wurde beschlossen</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>The Gibis, very smart thanks to their</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>The Gibis, very smart thanks to their</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>los Gibis a buscar transistores. Los</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>los Gibis a buscar transistores. Los</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>targad, said Shadokide plaanidele kiire</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>plantes poussant dans les jardins.</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>plantes poussant dans les jardins.</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>di mandare uno Shadok sul pianeta dei</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>トランジスタを出すたびに、彼らはシャドクより</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>транзистор іздеуге жіберу туралы шешім</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>텃밭 중 하나에 들어오게 두었지만,</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Jie leido Šadokui patekti į vieną iš sa</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>plānus un nolēma pajokot. Viņi ļāva</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>zoeken. De Gibis, die dankzij hun hoede</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>tranzystorów. Gibi, bardzo mądrzy</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>procurar transístores. Os Gibis, muito</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>transistores. Os Gibis, muito</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>дуже розумні завдяки своїм капелюхам,</t>
+        </is>
+      </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>但从四面八方包围了他，</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>但從四面八方包圍了他，</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -15129,6 +20989,116 @@
           <t>постоянно кончаясь неудачами.</t>
         </is>
       </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>пастаянна заканчваючыся няўдачамі.</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>werden fortgesetzt und enden</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>constantly ending in failure. This is</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>constantly ending in failure. This is</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>continúan, terminando constantemente en</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>continúan, terminando constantemente en</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>lõppedes pidevalt ebaõnnestumistega.</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>se poursuivent, se soldant</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>se poursuivent, se soldant</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>continuano, finendo costantemente in</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>終わっています。これはシャドク論理の</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>үнемі сәтсіздікпен аяқталуда. Мұның</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>실패로 돌아갑니다. 이는 샤독 논리의</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>baigiasi nesėkmėmis. Tai kyla iš vieno</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>beidzoties ar neveiksmēm. Tas ir saistī</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>eindigen voortdurend in mislukkingen.</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>kończąc się porażkami. Wynika to z</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>continuam, terminando constantemente em</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>continuam, terminando constantemente em</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>постійно закінчуючись невдачами.</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>结果不断以失败告终。</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>結果不斷以失敗告終。</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -15136,6 +21106,116 @@
           <t>принципов шадокской логики: «Нет</t>
         </is>
       </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>прынцыпаў шадоцкай логікі: «Няма</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>einem der Grundprinzipien der</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Shadok logic: ‘There is nothing that</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Shadok logic: ‘There is nothing that</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>principios básicos de la lógica Shadok:</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>principios básicos de la lógica Shadok:</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>põhiprintsiibist: „Pole olemas midagi,</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>repose sur l'un des principes de base</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>repose sur l'un des principes de base</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>principi base della logica Shadok:</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>『成功せずに無限に続くものなど存在しない』</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>қағидаларының бірінде: «Сәтсіздікке</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>않고 무한히 계속되는 것은 없다’</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>„Nėra nieko, kas tęstųsi be pabaigos</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>„Nav nekā tāda, kas turpinātos bezgalīg</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>van de Shadok-logica: ‚Er is niets dat</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>Shadoków: „Nie ma nic, co trwałoby</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>princípios básicos da lógica Shadok:</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>princípios básicos da lógica Shadok:</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>принципів шадоцької логіки: «Немає</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>‘没有什么是会无限持续且不以成功告终的’。</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>‘沒有什麼是會無限持續且不以成功告終的’。</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -15143,6 +21223,116 @@
           <t>ракета еще несовершенна, но они</t>
         </is>
       </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>што яно запрацуе». Іх ракета яшчэ</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>größer die Chance, dass es funktioniert</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>imperfect, but they have calculated</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>imperfect, but they have calculated</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>funcione». Su cohete aún es imperfecto,</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>funcione». Su cohete aún es imperfecto,</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>ebatäiuslik, kuid nad on välja</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>chances que ça marche ». Leur fusée</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>chances que ça marche ». Leur fusée</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>probabilità ci sono che funzioni».</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>あると計算しました…そして彼らは、999999回の</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>зымыраны әлі кемел емес, бірақ олар</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>100만 분의 1은 된다고 계산했습니다…</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>turi bent vieną šansą iš milijono, kad</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>izskaitļojuši, ka viņiem ir vismaz vien</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>onvolmaakt, maar ze hebben berekend dat</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>nieidealna, ale obliczyli, że mają</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>funcionar». O seu foguete ainda é</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>funcione». Seu foguete ainda é</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>ще недосконала, але вони вирахували, що</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>成功概率……</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>成功機率……</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -15150,6 +21340,116 @@
           <t>растений, произрастающих на огородах.</t>
         </is>
       </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>раслін, якія растуць на агародах.</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>mangelt. Doch bei den Gibis werden</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>It is decided to send a Shadok to the</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>It is decided to send a Shadok to the</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>plantas que crecen en los huertos. Se</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>plantas que crecen en los huertos. Se</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Gibide planeedile transistore otsima.</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>sécurité. Mais chez les Gibis, les</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>sécurité. Mais chez les Gibis, les</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>i transistor si raccolgono dalle piante</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>しました。彼らはシャドクを畑の一つに侵入させ</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>бақшаларда өсетін өсімдіктерден жиналад</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>기비들은 샤독의 계획을 금세 알아채고</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>savo skrybėlių, greitai perprato Šadokų</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>tranzistorus. Gibi, pateicoties savām</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>besloten om een Shadok naar de planeet</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>Postanowiono wysłać jednego z Shadoków</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>crescem nas hortas. Decidiu-se enviar u</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>crescem em hortas. Decidiu-se enviar um</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Вирішено послати одного з шадоків на</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>并决定戏弄他们。</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>並決定戲弄他們。</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -15157,6 +21457,104 @@
           <t>решили позабавиться. Они позволили</t>
         </is>
       </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>шадокаў і вырашылі пазабаўляцца. Яны</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Die Gibis, die dank ihrer Hüte sehr</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>They let the Shadok enter one of their</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>They let the Shadok enter one of their</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>planes de los Shadoks y decidieron</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>planes de los Shadoks y decidieron</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piirasid ta igast küljest ümber ja iga </t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>transistors. Les Gibis, très intelligen</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>transistors. Les Gibis, très intelligen</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>cappelli, hanno rapidamente intuito i</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>жоспарын тез түсініп, көңіл көтеруді</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>그들은 샤독보다 먼저 수확하려고</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>duoda tranzistorį, jie puola rinkti</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>kad augs uzzied un dod tranzistoru,</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>zich te amuseren. Ze lieten de Shadok t</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>się zabawić. Pozwolili Shadokowi</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Shadoks e decidiram divertir-se. Deixar</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Shadoks e decidiram se divertir. Eles</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>шадоку забратися в один із їхніх</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr"/>
+      <c r="Y183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -15171,6 +21569,76 @@
           <t>собрать урожай прежде шадока.</t>
         </is>
       </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>каб сабраць ураджай раней за шадока.</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>umzingelten ihn von allen Seiten. Jedes</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>cosecha antes que el Shadok.</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>cosecha antes que el Shadok.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>l'ont entouré de toutes parts, et à</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>l'ont entouré de toutes parts, et à</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>pianta fiorisce e produce un transistor</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>бұрын жинап алуға ұмтылады.</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr"/>
+      <c r="P185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>Shadok binnen te halen.</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>przed Shadokiem.</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>colheita antes do Shadok.</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>para colher antes do Shadok.</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr"/>
+      <c r="X185" t="inlineStr"/>
+      <c r="Y185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -15178,6 +21646,116 @@
           <t>терпят неудачу потому, что не хватает</t>
         </is>
       </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>церпяць няўдачу таму, што не хапае</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Der große Zauberer sagte, dass die</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>transistors in the safety systems.</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>transistors in the safety systems.</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>fallan porque faltan transistores en</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>fallan porque faltan transistores en</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>transistore. Kuid Gibid korjavad</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Le Grand Sorcier a dit que les fusées</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Le Grand Sorcier a dit que les fusées</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Il Grande Stregone ha detto che i razzi</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>トランジスタを探させることにしました。</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>ұшырауына қауіпсіздік жүйелеріндегі</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>수확합니다. 샤독 중 한 명을 기비의</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>augančių augalų. Nuspręsta nusiųsti</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>tranzistorus vāc no dārzos augošiem</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>veiligheidssystemen zitten. Maar bij de</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>tranzystorów w systemach bezpieczeństwa</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>falham porque faltam transístores nos</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>porque faltam transistores nos sistemas</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>транзисторів у системах безпеки.</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>寻找晶体管。</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>尋找電晶體。</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -15185,6 +21763,116 @@
           <t>транзисторов в системах безопасности.</t>
         </is>
       </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>транзістараў у сістэмах бяспекі.</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Raketen versagen, weil es an</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>But the Gibis harvest transistors from</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>But the Gibis harvest transistors from</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>los sistemas de seguridad. Pero los</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>los sistemas de seguridad. Pero los</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>transistore aedades kasvavatelt</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>échouent parce qu'il manque des</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>échouent parce qu'il manque des</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>falliscono perché mancano transistor</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>帽子のおかげで非常に賢いギビは、すぐに</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>транзисторлардың жетіспеушілігі себеп</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>행성으로 보내 트랜지스터를 찾아오기로</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>vieną Šadoką į Gibių planetą ieškoti</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>augiem. Ir nolemts nosūtīt vienu no</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>Gibis worden transistoren geoogst van</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>Ale u Gibich tranzystory zbiera się z</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>sistemas de segurança. Mas nos Gibis os</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>de segurança. Mas, para os Gibis, os</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Але у гібі транзистори збирають із</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>吉比人凭借他们的帽子非常聪明，</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>吉比人憑藉他們的帽子非常聰明，</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -15192,6 +21880,104 @@
           <t>шадоку забраться в один из их огородов,</t>
         </is>
       </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>дазволілі шадоку забрацца ў адзін з</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>intelligent sind, durchschauten schnell</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>gardens, but surrounded him, and every</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>gardens, but surrounded him, and every</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>divertirse. Dejaron que el Shadok</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>divertirse. Dejaron que el Shadok</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>kui taim õitseb ja annab transistori,</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>grâce à leurs chapeaux, ont rapidement</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>grâce à leurs chapeaux, ont rapidement</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>piani degli Shadok e hanno deciso di</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>ұйғарды. Олар шадокқа өз бақтарының</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>달려갑니다.</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>derliaus anksčiau už Šadoką.</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>viņi steidzas novākt ražu pirms Šadoka.</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>tot een van hun tuinen, maar omsingelde</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>wejść do jednego z ich ogródków, ale</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>o Shadok entrar numa das suas hortas,</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>deixaram o Shadok entrar em uma de suas</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>городів, але оточили його з усіх боків,</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr"/>
+      <c r="Y188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -15451,6 +22237,116 @@
           <t xml:space="preserve">  Жак Руксель. Великолепие навыворот.</t>
         </is>
       </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Жак Руксель. Веліч навыварат.</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>sein, dass der millionste funktioniert.</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Paris, Grasset Publishing.</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Paris, Grasset Publishing.</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Jacques Rouxel. La perfección al revés.</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Jacques Rouxel. La perfección al revés.</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Pariis, kirjastus Grasset.</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>fonctionne. »</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>fonctionne. »</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>milionesimo funzioni».</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>言いました。しかし、ギビのトランジスタは</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>Жак Руксель. Керісінше жетістік.</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>안전 시스템에 트랜지스터가 부족하기</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>patiria nesėkmę, nes saugos sistemose</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>Lielais burvis teica, ka raķetes cieš</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>Parijs, uitgeverij Grasset.</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>Paryż, wydawnictwo Grasset.</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>Jacques Rouxel. A perfeição ao contrári</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>Jacques Rouxel. A perfeição ao contrári</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>Париж, видавництво Грассе.</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>但在吉比星，晶体管是从</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>但在吉比星，電晶體是從</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -16473,6 +23369,116 @@
           <t>«У шадоков ситуация удовлетворительна.</t>
         </is>
       </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>«У шадокаў сітуацыя здавальняючая.</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>„Die Situation der Shadoks ist</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>“The situation of the Shadoks is</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>“The situation of the Shadoks is</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>«La situación de los Shadoks es</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>«La situación de los Shadoks es</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>„Shadokide olukord on rahuldav.</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>« La situation des Shadoks est</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>« La situation des Shadoks est</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>«La situazione degli Shadok è</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>「シャドクの状況は満足のいくものです。</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>«Шадоктардың жағдайы қанағаттанарлық.</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>«샤독의 상황은 만족스럽습니다.</t>
+        </is>
+      </c>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>„Šadokų situacija yra patenkinama.</t>
+        </is>
+      </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>„Šadoku situācija ir apmierinoša.</t>
+        </is>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>„De situatie van de Shadoks is</t>
+        </is>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>„Sytuacja Shadoków jest zadowalająca.</t>
+        </is>
+      </c>
+      <c r="T371" t="inlineStr">
+        <is>
+          <t>«A situação dos Shadoks é</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr">
+        <is>
+          <t>«A situação dos Shadoks é</t>
+        </is>
+      </c>
+      <c r="W371" t="inlineStr">
+        <is>
+          <t>«У шадоків ситуація задовільна.</t>
+        </is>
+      </c>
+      <c r="X371" t="inlineStr">
+        <is>
+          <t>“沙多克的处境尚可。</t>
+        </is>
+      </c>
+      <c r="Y371" t="inlineStr">
+        <is>
+          <t>“沙多克的處境尚可。</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -17901,6 +24907,116 @@
           <t xml:space="preserve">    Великий колдун сказал, что ракеты</t>
         </is>
       </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Вялікі чараўнік сказаў, што ракеты</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Paris, Éditions Grasset.</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>fail because there are not enough</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>fail because there are not enough</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>El Gran Hechicero dijo que los cohetes</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>El Gran Hechicero dijo que los cohetes</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>sest turvasüsteemides pole piisavalt</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>Paris, Éditions Grasset.</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Paris, Éditions Grasset.</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>contrario. Parigi, Edizioni Grasset.</t>
+        </is>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>シャドクの一人をギビの惑星に送り、</t>
+        </is>
+      </c>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>Ұлы сиқыршы зымырандардың сәтсіздікке</t>
+        </is>
+      </c>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>텃밭에서 자라는 식물에서 트랜지스터를</t>
+        </is>
+      </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>tranzistoriai renkami nuo daržuose</t>
+        </is>
+      </c>
+      <c r="Q575" t="inlineStr">
+        <is>
+          <t>trūkst tranzistoru. Taču pie Gibi</t>
+        </is>
+      </c>
+      <c r="R575" t="inlineStr">
+        <is>
+          <t>omdat er niet genoeg transistoren in de</t>
+        </is>
+      </c>
+      <c r="S575" t="inlineStr">
+        <is>
+          <t>ponoszą porażkę, ponieważ brakuje</t>
+        </is>
+      </c>
+      <c r="T575" t="inlineStr">
+        <is>
+          <t>O Grande Feiticeiro disse que os foguet</t>
+        </is>
+      </c>
+      <c r="U575" t="inlineStr">
+        <is>
+          <t>O Grande Mago disse que os foguetes fal</t>
+        </is>
+      </c>
+      <c r="W575" t="inlineStr">
+        <is>
+          <t>зазнають невдачі тому, що не вистачає</t>
+        </is>
+      </c>
+      <c r="X575" t="inlineStr">
+        <is>
+          <t>沙多克决定派一名成员前往吉比星球</t>
+        </is>
+      </c>
+      <c r="Y575" t="inlineStr">
+        <is>
+          <t>沙多克決定派一名成員前往吉比星球</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -18160,6 +25276,116 @@
           <t>Испытания ракет продолжаются,</t>
         </is>
       </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Выпрабаванні ракет працягваюцца,</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>zufriedenstellend. Die Raketentests</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>satisfactory. Rocket tests continue,</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>satisfactory. Rocket tests continue,</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>satisfactoria. Las pruebas de cohetes</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>satisfactoria. Las pruebas de cohetes</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>Raketikatsetused jätkuvad,</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>satisfaisante. Les essais de fusées</t>
+        </is>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>satisfaisante. Les essais de fusées</t>
+        </is>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>soddisfacente. I test dei razzi</t>
+        </is>
+      </c>
+      <c r="M612" t="inlineStr">
+        <is>
+          <t>ロケットの試験は続き、絶え間なく失敗に</t>
+        </is>
+      </c>
+      <c r="N612" t="inlineStr">
+        <is>
+          <t>Зымыран сынақтары жалғасуда және</t>
+        </is>
+      </c>
+      <c r="O612" t="inlineStr">
+        <is>
+          <t>로켓 실험은 계속되고 있으며, 끊임없이</t>
+        </is>
+      </c>
+      <c r="P612" t="inlineStr">
+        <is>
+          <t>Raketų bandymai tęsiasi ir nuolat</t>
+        </is>
+      </c>
+      <c r="Q612" t="inlineStr">
+        <is>
+          <t>Raķešu izmēģinājumi turpinās, pastāvīgi</t>
+        </is>
+      </c>
+      <c r="R612" t="inlineStr">
+        <is>
+          <t>bevredigend. Raketproeven gaan door en</t>
+        </is>
+      </c>
+      <c r="S612" t="inlineStr">
+        <is>
+          <t>Testy rakiet trwają, nieustannie</t>
+        </is>
+      </c>
+      <c r="T612" t="inlineStr">
+        <is>
+          <t>satisfatória. Os testes de foguetes</t>
+        </is>
+      </c>
+      <c r="U612" t="inlineStr">
+        <is>
+          <t>satisfatória. Os testes de foguetes</t>
+        </is>
+      </c>
+      <c r="W612" t="inlineStr">
+        <is>
+          <t>Випробування ракет тривають,</t>
+        </is>
+      </c>
+      <c r="X612" t="inlineStr">
+        <is>
+          <t>火箭试验仍在继续，</t>
+        </is>
+      </c>
+      <c r="Y612" t="inlineStr">
+        <is>
+          <t>火箭試驗仍在繼續，</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -18650,6 +25876,116 @@
           <t xml:space="preserve">    Дело здесь в одном из основных</t>
         </is>
       </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Справа тут у адным з асноўных</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>ständig in Misserfolgen. Dies liegt an</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>due to one of the basic principles of</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>due to one of the basic principles of</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>fracasos. Esto se debe a uno de los</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>fracasos. Esto se debe a uno de los</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>See tuleneb ühest Shadokide loogika</t>
+        </is>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>constamment par des échecs. Cela</t>
+        </is>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>constamment par des échecs. Cela</t>
+        </is>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>fallimenti. Ciò è dovuto a uno dei</t>
+        </is>
+      </c>
+      <c r="M682" t="inlineStr">
+        <is>
+          <t>基本原則の一つによるものです。つまり、</t>
+        </is>
+      </c>
+      <c r="N682" t="inlineStr">
+        <is>
+          <t>себебі шадок логикасының негізгі</t>
+        </is>
+      </c>
+      <c r="O682" t="inlineStr">
+        <is>
+          <t>기본 원칙 중 하나인 ‘성공으로 끝나지</t>
+        </is>
+      </c>
+      <c r="P682" t="inlineStr">
+        <is>
+          <t>pagrindinių Šadokų logikos principų:</t>
+        </is>
+      </c>
+      <c r="Q682" t="inlineStr">
+        <is>
+          <t>ar vienu no Šadoku loģikas pamatprincip</t>
+        </is>
+      </c>
+      <c r="R682" t="inlineStr">
+        <is>
+          <t>Dit komt door een van de basisprincipes</t>
+        </is>
+      </c>
+      <c r="S682" t="inlineStr">
+        <is>
+          <t>jednej z podstawowych zasad logiki</t>
+        </is>
+      </c>
+      <c r="T682" t="inlineStr">
+        <is>
+          <t>fracassos. Isto deve-se a um dos</t>
+        </is>
+      </c>
+      <c r="U682" t="inlineStr">
+        <is>
+          <t>fracassos. Isso se deve a um dos</t>
+        </is>
+      </c>
+      <c r="W682" t="inlineStr">
+        <is>
+          <t>Справа тут в одному з основних</t>
+        </is>
+      </c>
+      <c r="X682" t="inlineStr">
+        <is>
+          <t>这源于沙多克逻辑的基本原则之一：</t>
+        </is>
+      </c>
+      <c r="Y682" t="inlineStr">
+        <is>
+          <t>這源於沙多克邏輯的基本原則之一：</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -19280,6 +26616,116 @@
           <t>Но у гиби транзисторы собирают с</t>
         </is>
       </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>Але ў гібі транзістары збіраюць з</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>Transistoren in den Sicherheitssystemen</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>plants that grow in their gardens.</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>plants that grow in their gardens.</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>Gibis recogen transistores de las</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>Gibis recogen transistores de las</t>
+        </is>
+      </c>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>taimedelt. Otsustatakse saata üks Shado</t>
+        </is>
+      </c>
+      <c r="J772" t="inlineStr">
+        <is>
+          <t>transistors dans les systèmes de</t>
+        </is>
+      </c>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>transistors dans les systèmes de</t>
+        </is>
+      </c>
+      <c r="L772" t="inlineStr">
+        <is>
+          <t>nei sistemi di sicurezza. Ma dai Gibi</t>
+        </is>
+      </c>
+      <c r="M772" t="inlineStr">
+        <is>
+          <t>シャドクの計画を見抜き、楽しむことに</t>
+        </is>
+      </c>
+      <c r="N772" t="inlineStr">
+        <is>
+          <t>деді. Бірақ гибилерде транзисторлар</t>
+        </is>
+      </c>
+      <c r="O772" t="inlineStr">
+        <is>
+          <t>결정했습니다. 모자 덕분에 매우 똑똑한</t>
+        </is>
+      </c>
+      <c r="P772" t="inlineStr">
+        <is>
+          <t>tranzistorių. Gibiai, labai protingi dė</t>
+        </is>
+      </c>
+      <c r="Q772" t="inlineStr">
+        <is>
+          <t>Šadokiem uz Gibi planētu meklēt</t>
+        </is>
+      </c>
+      <c r="R772" t="inlineStr">
+        <is>
+          <t>planten die in tuinen groeien. Er wordt</t>
+        </is>
+      </c>
+      <c r="S772" t="inlineStr">
+        <is>
+          <t>roślin rosnących w ogródkach.</t>
+        </is>
+      </c>
+      <c r="T772" t="inlineStr">
+        <is>
+          <t>transístores são colhidos de plantas qu</t>
+        </is>
+      </c>
+      <c r="U772" t="inlineStr">
+        <is>
+          <t>transistores são colhidos de plantas qu</t>
+        </is>
+      </c>
+      <c r="W772" t="inlineStr">
+        <is>
+          <t>рослин, що ростуть на городах.</t>
+        </is>
+      </c>
+      <c r="X772" t="inlineStr">
+        <is>
+          <t>很快就识破了沙多克的计划，</t>
+        </is>
+      </c>
+      <c r="Y772" t="inlineStr">
+        <is>
+          <t>很快就識破了沙多克的計畫，</t>
+        </is>
+      </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
@@ -21497,6 +28943,116 @@
       <c r="A1089" t="inlineStr">
         <is>
           <t>Решено послать одного из шадоков на</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>Вырашана паслаць аднаго з шадокаў на</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>Transistoren von Pflanzen geerntet, die</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>Gibis planet to find transistors.</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>Gibis planet to find transistors.</t>
+        </is>
+      </c>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>decide enviar a un Shadok al planeta de</t>
+        </is>
+      </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>decide enviar a un Shadok al planeta de</t>
+        </is>
+      </c>
+      <c r="I1089" t="inlineStr">
+        <is>
+          <t>Gibid, kes on tänu oma kübaratele väga</t>
+        </is>
+      </c>
+      <c r="J1089" t="inlineStr">
+        <is>
+          <t>transistors sont récoltés sur des</t>
+        </is>
+      </c>
+      <c r="K1089" t="inlineStr">
+        <is>
+          <t>transistors sont récoltés sur des</t>
+        </is>
+      </c>
+      <c r="L1089" t="inlineStr">
+        <is>
+          <t>che crescono negli orti. Viene deciso</t>
+        </is>
+      </c>
+      <c r="M1089" t="inlineStr">
+        <is>
+          <t>ましたが、彼を四方から囲み、植物が花を咲かせて</t>
+        </is>
+      </c>
+      <c r="N1089" t="inlineStr">
+        <is>
+          <t>Шадоктардың бірін гиби планетасына</t>
+        </is>
+      </c>
+      <c r="O1089" t="inlineStr">
+        <is>
+          <t>장난을 치기로 했습니다. 그들은 샤독이</t>
+        </is>
+      </c>
+      <c r="P1089" t="inlineStr">
+        <is>
+          <t>planus ir nusprendė pasilinksminti.</t>
+        </is>
+      </c>
+      <c r="Q1089" t="inlineStr">
+        <is>
+          <t>cepurēm ļoti gudri, ātri atkodē Šadoku</t>
+        </is>
+      </c>
+      <c r="R1089" t="inlineStr">
+        <is>
+          <t xml:space="preserve">van de Gibis te sturen om transistoren </t>
+        </is>
+      </c>
+      <c r="S1089" t="inlineStr">
+        <is>
+          <t>na planetę Gibich, by szukał</t>
+        </is>
+      </c>
+      <c r="T1089" t="inlineStr">
+        <is>
+          <t>Shadok ao planeta dos Gibis para</t>
+        </is>
+      </c>
+      <c r="U1089" t="inlineStr">
+        <is>
+          <t>Shadok ao planeta dos Gibis para buscar</t>
+        </is>
+      </c>
+      <c r="W1089" t="inlineStr">
+        <is>
+          <t>планету гібі шукати транзистори. Гібі,</t>
+        </is>
+      </c>
+      <c r="X1089" t="inlineStr">
+        <is>
+          <t>他们让沙多克进入了其中一个菜园，</t>
+        </is>
+      </c>
+      <c r="Y1089" t="inlineStr">
+        <is>
+          <t>他們讓沙多克進入了其中一個菜園，</t>
         </is>
       </c>
     </row>
